--- a/Configs/GameConfig/Datas/SoundConfig.xlsx
+++ b/Configs/GameConfig/Datas/SoundConfig.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1394,6 +1394,41 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Level1Bgm</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>花果山BGM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>花果山关卡背景音乐(关卡进场播放)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1_music.mp3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>res://TheGame/Audios/BGM/level_1.mp3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/SoundConfig.xlsx
+++ b/Configs/GameConfig/Datas/SoundConfig.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1394,41 +1394,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Level1Bgm</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>花果山BGM</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>花果山关卡背景音乐(关卡进场播放)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1_music.mp3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Music</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>res://TheGame/Audios/BGM/level_1.mp3</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/SoundConfig.xlsx
+++ b/Configs/GameConfig/Datas/SoundConfig.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1394,6 +1394,146 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MenuTheme</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>开始与选角音乐</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GGF 分组播放</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>zmxy_1BGM.mp3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>res://TheGame/Audios/Music/map_theme.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>101</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MapTheme</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>七魔王地图音乐</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GGF 分组播放</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>zmxy_1BGM.mp3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>res://TheGame/Audios/Music/map_theme.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>102</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HuaguoshanTheme</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>花果山音乐</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GGF 分组播放</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1_music.mp3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>res://TheGame/Audios/Music/huaguoshan_theme.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>103</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MenuConfirm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>菜单确认音</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GGF 分组播放</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>项目原创木质短音</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>res://TheGame/Audios/UI/menu_confirm.wav</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/SoundConfig.xlsx
+++ b/Configs/GameConfig/Datas/SoundConfig.xlsx
@@ -1,177 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd7aaa35e6614d7b"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="20">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,187 +156,156 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
@@ -400,7 +346,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,60 +564,59 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -907,7 +852,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -916,13 +861,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -956,17 +901,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1021,166 +955,160 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
-    <col width="33.1818181818182" customWidth="1" min="2" max="2"/>
-    <col width="42.1818181818182" customWidth="1" min="3" max="3"/>
-    <col width="17.3636363636364" customWidth="1" min="4" max="4"/>
-    <col width="24.1818181818182" customWidth="1" min="5" max="5"/>
-    <col width="27.5454545454545" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="60.1818181818182" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="8.545454978942871" customWidth="1"/>
+    <col min="2" max="2" width="33.181819915771484" customWidth="1"/>
+    <col min="3" max="3" width="42.181819915771484" customWidth="1"/>
+    <col min="4" max="4" width="17.363636016845703" customWidth="1"/>
+    <col min="5" max="5" width="24.18181800842285" customWidth="1"/>
+    <col min="6" max="6" width="27.545454025268555" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="60.181819915771484" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t xml:space="preserve">Id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t xml:space="preserve">Key</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t xml:space="preserve">NameCn</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t xml:space="preserve">Desc</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>LegacyId</t>
+          <t xml:space="preserve">LegacyId</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t xml:space="preserve">Group</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t xml:space="preserve">Path</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t xml:space="preserve">##type</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t xml:space="preserve">##group</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>音效ID(与 SoundId 枚举值一致)</t>
+          <t xml:space="preserve">音效ID(与 SoundId 枚举值一致)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>枚举名(与 SoundId 一致,便于读表/搜索)</t>
+          <t xml:space="preserve">枚举名(与 SoundId 一致,便于读表/搜索)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t xml:space="preserve">中文名</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t xml:space="preserve">描述</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>旧音频文件名</t>
+          <t xml:space="preserve">旧音频文件名</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>框架声音组名(Music/SFX/UI,对应 SoundGroupRes)</t>
+          <t xml:space="preserve">框架声音组名(Music/SFX/UI,对应 SoundGroupRes)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>音频资源路径</t>
+          <t xml:space="preserve">音频资源路径</t>
         </is>
       </c>
     </row>
@@ -1188,34 +1116,28 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>WukongAttack2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>悟空挥棍2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>普攻第2段起手；旧 40_Role1_hit1AndHit2 实际只被 hit2 用</t>
-        </is>
+      <c r="C6" t="str">
+        <v>WukongAttack1And2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>悟空挥棍1/2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>造一普攻第1、2段起手</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40_Role1_hit1AndHit2.mp3</t>
+          <t xml:space="preserve">40_Role1_hit1AndHit2.mp3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t xml:space="preserve">SFX</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/SFX/wukong/wukong_attack_2.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/SFX/wukong/wukong_attack_2.mp3</t>
         </is>
       </c>
     </row>
@@ -1223,34 +1145,28 @@
       <c r="B7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>WukongAttack1And3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>悟空挥棍1/3</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>普攻1、3段共用起手</t>
-        </is>
+      <c r="C7" t="str">
+        <v>WukongAttack3And4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>悟空挥棍3/4</v>
+      </c>
+      <c r="E7" t="str">
+        <v>造一普攻第3、4段起手</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39_Role1_hit3AndHit4.mp3</t>
+          <t xml:space="preserve">39_Role1_hit3AndHit4.mp3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t xml:space="preserve">SFX</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/SFX/wukong/wukong_attack_1_3.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/SFX/wukong/wukong_attack_1_3.mp3</t>
         </is>
       </c>
     </row>
@@ -1258,34 +1174,28 @@
       <c r="B8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>WukongAttack4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>悟空挥棍4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>普攻第4段起手</t>
-        </is>
+      <c r="C8" t="str">
+        <v>WukongAttack5</v>
+      </c>
+      <c r="D8" t="str">
+        <v>悟空挥棍5</v>
+      </c>
+      <c r="E8" t="str">
+        <v>造一普攻第5段终结起手</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38_Role1_hit5.mp3</t>
+          <t xml:space="preserve">38_Role1_hit5.mp3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t xml:space="preserve">SFX</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/SFX/wukong/wukong_attack_4.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/SFX/wukong/wukong_attack_4.mp3</t>
         </is>
       </c>
     </row>
@@ -1295,32 +1205,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WukongHurt</t>
+          <t xml:space="preserve">WukongHurt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>悟空受击语音</t>
+          <t xml:space="preserve">悟空受击语音</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>悟空自己挨打时的语音(按受害者选音,BaseHero.gd:592)</t>
+          <t xml:space="preserve">悟空自己挨打时的语音(按受害者选音,BaseHero.gd:592)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49_Role1_beAttack.mp3</t>
+          <t xml:space="preserve">49_Role1_beAttack.mp3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t xml:space="preserve">SFX</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/SFX/wukong/wukong_hurt.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/SFX/wukong/wukong_hurt.mp3</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1240,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WukongDeath</t>
+          <t xml:space="preserve">WukongDeath</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>悟空死亡语音</t>
+          <t xml:space="preserve">悟空死亡语音</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>悟空死亡</t>
+          <t xml:space="preserve">悟空死亡</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59_Role1_dead.mp3</t>
+          <t xml:space="preserve">59_Role1_dead.mp3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t xml:space="preserve">SFX</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/SFX/wukong/wukong_death.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/SFX/wukong/wukong_death.mp3</t>
         </is>
       </c>
     </row>
@@ -1365,32 +1275,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WukongImpact</t>
+          <t xml:space="preserve">WukongImpact</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>悟空命中音</t>
+          <t xml:space="preserve">悟空命中音</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>悟空的棍打中东西的命中音(按攻击者选音,BaseMonster.gd:652)</t>
+          <t xml:space="preserve">悟空的棍打中东西的命中音(按攻击者选音,BaseMonster.gd:652)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6_BeattackByRole1.mp3</t>
+          <t xml:space="preserve">6_BeattackByRole1.mp3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t xml:space="preserve">SFX</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/SFX/wukong/wukong_hit_impact.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/SFX/wukong/wukong_hit_impact.mp3</t>
         </is>
       </c>
     </row>
@@ -1400,32 +1310,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MenuTheme</t>
+          <t xml:space="preserve">MenuTheme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>开始与选角音乐</t>
+          <t xml:space="preserve">开始与选角音乐</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GGF 分组播放</t>
+          <t xml:space="preserve">GGF 分组播放</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>zmxy_1BGM.mp3</t>
+          <t xml:space="preserve">zmxy_1BGM.mp3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t xml:space="preserve">Music</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/Music/map_theme.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/Music/map_theme.mp3</t>
         </is>
       </c>
     </row>
@@ -1435,32 +1345,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MapTheme</t>
+          <t xml:space="preserve">MapTheme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>七魔王地图音乐</t>
+          <t xml:space="preserve">七魔王地图音乐</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GGF 分组播放</t>
+          <t xml:space="preserve">GGF 分组播放</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>zmxy_1BGM.mp3</t>
+          <t xml:space="preserve">zmxy_1BGM.mp3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t xml:space="preserve">Music</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/Music/map_theme.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/Music/map_theme.mp3</t>
         </is>
       </c>
     </row>
@@ -1470,32 +1380,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HuaguoshanTheme</t>
+          <t xml:space="preserve">HuaguoshanTheme</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>花果山音乐</t>
+          <t xml:space="preserve">花果山音乐</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GGF 分组播放</t>
+          <t xml:space="preserve">GGF 分组播放</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1_music.mp3</t>
+          <t xml:space="preserve">1_music.mp3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t xml:space="preserve">Music</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/Music/huaguoshan_theme.mp3</t>
+          <t xml:space="preserve">res://TheGame/Audios/Music/huaguoshan_theme.mp3</t>
         </is>
       </c>
     </row>
@@ -1505,36 +1415,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MenuConfirm</t>
+          <t xml:space="preserve">MenuConfirm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>菜单确认音</t>
+          <t xml:space="preserve">菜单确认音</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GGF 分组播放</t>
+          <t xml:space="preserve">GGF 分组播放</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>项目原创木质短音</t>
+          <t xml:space="preserve">项目原创木质短音</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t xml:space="preserve">UI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>res://TheGame/Audios/UI/menu_confirm.wav</t>
+          <t xml:space="preserve">res://TheGame/Audios/UI/menu_confirm.wav</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/SoundConfig.xlsx
+++ b/Configs/GameConfig/Datas/SoundConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd7aaa35e6614d7b"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f1b63e96bf24f5c"/>
   </sheets>
 </workbook>
 </file>
@@ -1444,6 +1444,174 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="str">
+        <v>WukongRisingDragon</v>
+      </c>
+      <c r="D16" t="str">
+        <v>悟空升龙斩</v>
+      </c>
+      <c r="E16" t="str">
+        <v>造一原版技能音效；由 GGF SFX 播放</v>
+      </c>
+      <c r="F16" t="str">
+        <v>official.Music.Role1_hit8</v>
+      </c>
+      <c r="G16" t="str">
+        <v>SFX</v>
+      </c>
+      <c r="H16" t="str">
+        <v>res://TheGame/Audios/SFX/wukong/skills/wukong_rising_dragon.mp3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="str">
+        <v>WukongFlameThrust</v>
+      </c>
+      <c r="D17" t="str">
+        <v>悟空火炎突击</v>
+      </c>
+      <c r="E17" t="str">
+        <v>造一原版技能音效；由 GGF SFX 播放</v>
+      </c>
+      <c r="F17" t="str">
+        <v>official.Music.Role1_hit6</v>
+      </c>
+      <c r="G17" t="str">
+        <v>SFX</v>
+      </c>
+      <c r="H17" t="str">
+        <v>res://TheGame/Audios/SFX/wukong/skills/wukong_flame_thrust.mp3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="str">
+        <v>WukongBlazingFlash</v>
+      </c>
+      <c r="D18" t="str">
+        <v>悟空烈焰闪</v>
+      </c>
+      <c r="E18" t="str">
+        <v>造一原版技能音效；由 GGF SFX 播放</v>
+      </c>
+      <c r="F18" t="str">
+        <v>official.Music.Role1_hit7</v>
+      </c>
+      <c r="G18" t="str">
+        <v>SFX</v>
+      </c>
+      <c r="H18" t="str">
+        <v>res://TheGame/Audios/SFX/wukong/skills/wukong_blazing_flash.mp3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="str">
+        <v>WukongFlameStorm</v>
+      </c>
+      <c r="D19" t="str">
+        <v>悟空烈焰风暴</v>
+      </c>
+      <c r="E19" t="str">
+        <v>造一原版技能音效；由 GGF SFX 播放</v>
+      </c>
+      <c r="F19" t="str">
+        <v>official.Music.Role1_hit9</v>
+      </c>
+      <c r="G19" t="str">
+        <v>SFX</v>
+      </c>
+      <c r="H19" t="str">
+        <v>res://TheGame/Audios/SFX/wukong/skills/wukong_flame_storm.mp3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="str">
+        <v>WukongFireDemonStart</v>
+      </c>
+      <c r="D20" t="str">
+        <v>悟空火魔斩起手</v>
+      </c>
+      <c r="E20" t="str">
+        <v>造一原版技能音效；由 GGF SFX 播放</v>
+      </c>
+      <c r="F20" t="str">
+        <v>official.Music.Role1_hit10_1</v>
+      </c>
+      <c r="G20" t="str">
+        <v>SFX</v>
+      </c>
+      <c r="H20" t="str">
+        <v>res://TheGame/Audios/SFX/wukong/skills/wukong_fire_demon_start.mp3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="str">
+        <v>WukongFireDemonCombo</v>
+      </c>
+      <c r="D21" t="str">
+        <v>悟空火魔九连斩</v>
+      </c>
+      <c r="E21" t="str">
+        <v>造一原版技能音效；由 GGF SFX 播放</v>
+      </c>
+      <c r="F21" t="str">
+        <v>official.Music.Role1_hit10_2</v>
+      </c>
+      <c r="G21" t="str">
+        <v>SFX</v>
+      </c>
+      <c r="H21" t="str">
+        <v>res://TheGame/Audios/SFX/wukong/skills/wukong_fire_demon_combo.mp3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" t="str">
+        <v>WukongFireDemonLanding</v>
+      </c>
+      <c r="D22" t="str">
+        <v>悟空火魔斩落地</v>
+      </c>
+      <c r="E22" t="str">
+        <v>造一原版技能音效；由 GGF SFX 播放</v>
+      </c>
+      <c r="F22" t="str">
+        <v>official.Music.Role1_hit10_3</v>
+      </c>
+      <c r="G22" t="str">
+        <v>SFX</v>
+      </c>
+      <c r="H22" t="str">
+        <v>res://TheGame/Audios/SFX/wukong/skills/wukong_fire_demon_landing.mp3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
